--- a/data/trans_dic/P32E$eventos_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32E$eventos_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos</t>
+          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,55</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,01</t>
+          <t>0,0; 4,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,74</t>
+          <t>0,0; 21,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,26</t>
+          <t>0,0; 5,22</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,67</t>
+          <t>0,0; 23,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 34,9</t>
+          <t>3,88; 40,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 25,82</t>
+          <t>4,45; 26,82</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,91</t>
+          <t>0,59; 5,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 23,68</t>
+          <t>2,26; 21,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 8,07</t>
+          <t>1,64; 8,18</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos</t>
+          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1520</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1033</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1459</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4587</t>
+          <t>0; 4465</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4760</t>
+          <t>0; 4971</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6025</t>
+          <t>0; 5983</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7246</t>
+          <t>0; 5878</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1061; 9128</t>
+          <t>1014; 10597</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2216; 13279</t>
+          <t>2289; 13789</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>885; 8513</t>
+          <t>849; 8139</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1221; 12806</t>
+          <t>1225; 11857</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3212; 15977</t>
+          <t>3256; 16205</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$eventos_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32E$eventos_2023-Estudios-trans_dic.xlsx
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,87</t>
+          <t>0,0; 5,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,66</t>
+          <t>0,0; 19,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,22</t>
+          <t>0,0; 4,81</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,26</t>
+          <t>0,0; 27,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 40,52</t>
+          <t>3,72; 36,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,45; 26,82</t>
+          <t>4,14; 24,24</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,65</t>
+          <t>0,58; 5,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 21,92</t>
+          <t>2,57; 19,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 8,18</t>
+          <t>1,35; 7,23</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1999</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4465</t>
+          <t>0; 6263</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4971</t>
+          <t>0; 5771</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5983</t>
+          <t>0; 6468</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6157</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5878</t>
+          <t>0; 7504</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1014; 10597</t>
+          <t>1026; 10107</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2289; 13789</t>
+          <t>2255; 13211</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>8157</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>849; 8139</t>
+          <t>935; 8179</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1225; 11857</t>
+          <t>1633; 12407</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3256; 16205</t>
+          <t>3019; 16202</t>
         </is>
       </c>
     </row>
